--- a/data/employees/EMP078/AST-EMP078-06.xlsx
+++ b/data/employees/EMP078/AST-EMP078-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shift Productivity Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,199 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Shift Productivity Report - Jamie Brown (Operations)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jamie Brown | Role: Specialist | Location: Portland | Date: 2025-04-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>99</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>87</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Shift</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Efficiency %</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>67</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>EMP078</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Team Lead A</t>
+          <t>Ast Emp078 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>96</v>
+        <v>72</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>EMP078</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Team Lead B</t>
+          <t>Ast Emp078 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>Innovation</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>102</v>
+        <v>73</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Night</t>
+          <t>EMP078</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Team Lead C</t>
+          <t>Ast Emp078 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G7" t="n">
         <v>92</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>EMP078</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead D</t>
+          <t>Ast Emp078 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>Velocity</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
-      </c>
-      <c r="F8" t="n">
-        <v>9500</v>
-      </c>
-      <c r="G8" t="n">
-        <v>96.8</v>
+        <v>85</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>90</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>95</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>90</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>63</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>83</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>95</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>82</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>68</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>62</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>87</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>79</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>86</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>63</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>65</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp078 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>97</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP078</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP078 contributes to ast emp078 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>